--- a/output/full_scan/batch_seq1_2026-08-31.xlsx
+++ b/output/full_scan/batch_seq1_2026-08-31.xlsx
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>235.6610551174354</v>
+        <v>235.6610551174353</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>16.3</v>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>202.2903562681362</v>
+        <v>202.2903562681361</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>17.3</v>

--- a/output/full_scan/batch_seq1_2026-08-31.xlsx
+++ b/output/full_scan/batch_seq1_2026-08-31.xlsx
@@ -527,54 +527,54 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1563</v>
+        <v>1303</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1040.629404870625</v>
+        <v>1156.081590957765</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>66</v>
+        <v>242.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.98512603201439</v>
+        <v>68.46571094612244</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>17.57465384118926</v>
+        <v>17.02720855780595</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.194834990775525</v>
+        <v>1.680660399337297</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.6475740028015573</v>
+        <v>4.2871701521968</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>794.7428316337279</v>
+        <v>1114.835727194349</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>68.3</v>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>64.59036314746766</v>
+        <v>64.59036315054379</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13.95795699209078</v>
+        <v>13.95795707771139</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.73846087213538</v>
+        <v>2.746229147438261</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,11 +623,11 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.8618398912868017</v>
+        <v>0.8618398911723237</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>776.6217547756481</v>
+        <v>1096.621754775648</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>66.2</v>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.57064355143171</v>
+        <v>66.57064355915378</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>17.55888511282274</v>
+        <v>17.55888517430792</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.234085536670473</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,51 +676,51 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.8095288288789912</v>
+        <v>0.8095288287645133</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1440</v>
+        <v>1563</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>763.7755777063761</v>
+        <v>1030.629404870625</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13.9</v>
+        <v>66</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>60.33210099499578</v>
+        <v>59.98512606370167</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>23.3615375936173</v>
+        <v>17.57465394946664</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.556168426689001</v>
+        <v>2.194834990775525</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0460140370207641</v>
+        <v>0.6475740027294555</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1303</v>
+        <v>1312</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>740.575878701506</v>
+        <v>958.4861558076844</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>242.5</v>
+        <v>15.55</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>68.4657109474352</v>
+        <v>77.03027019982576</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>17.02720849431544</v>
+        <v>20.27059654228194</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.643757201441768</v>
+        <v>5.368893575927915</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.2871701522731</v>
+        <v>0.4268824328235377</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>728.4861558076844</v>
+        <v>937.8447618928662</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>15.55</v>
+        <v>14.4</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>77.03027017051002</v>
+        <v>60.02240055844257</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>20.27059645082356</v>
+        <v>22.23873431612888</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>5.368893575927915</v>
+        <v>2.179262391148988</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4268824328540623</v>
+        <v>0.1119048136698203</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>709.037244103249</v>
+        <v>765.1979049795432</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14.4</v>
+        <v>12.65</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>60.02240052399359</v>
+        <v>56.66296417213531</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.23873417865373</v>
+        <v>14.19582085215228</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.856221844807222</v>
+        <v>1.983128980355958</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1119048137079795</v>
+        <v>0.1194854751853456</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1101</v>
+        <v>1440</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>699</v>
+        <v>763.7755777063762</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>24.4</v>
+        <v>13.9</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>52.17736432943659</v>
+        <v>60.33210104166854</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>24.04143576729002</v>
+        <v>23.36153758968609</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>10.02176299692041</v>
+        <v>1.556168426689001</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.0255841595884104</v>
+        <v>0.0460140369635254</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1402</v>
+        <v>1305</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>654.0112254212297</v>
+        <v>745.7341275304628</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>28.35</v>
+        <v>12.55</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>52.876586549629</v>
+        <v>58.13699607822074</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>21.17613816184535</v>
+        <v>13.43374860406694</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.7926473338355456</v>
+        <v>1.658078408327871</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0214796118666765</v>
+        <v>0.1193963203617528</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>649.8608423287941</v>
+        <v>708.1908136414735</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>66</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.3827201026432</v>
+        <v>61.8855449381302</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>32.15871546355537</v>
+        <v>33.96063664676095</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8049966439350292</v>
+        <v>0.4529857442042004</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.007150373343975</v>
+        <v>0.1868735322181849</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1304</v>
+        <v>1101</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>625.1979049795424</v>
+        <v>699</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12.65</v>
+        <v>24.4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>56.66296413421242</v>
+        <v>52.17736438460241</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>14.19582077421156</v>
+        <v>24.04143591603973</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.983128980355958</v>
+        <v>10.59582199429252</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.119485475225412</v>
+        <v>-0.0255841596838073</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1558</v>
+        <v>1455</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>595.7336306125093</v>
+        <v>698.0249463490826</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>103.5</v>
+        <v>10</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>68.1576257116017</v>
+        <v>59.93406250478998</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.85519630442882</v>
+        <v>26.46327997211575</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.7450592151670029</v>
+        <v>0.6335752630899438</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.3419629452599833</v>
+        <v>0.014036081862678</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1455</v>
+        <v>1313</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>588.0249463490825</v>
+        <v>675.3299316585474</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10</v>
+        <v>12.15</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>59.93406251465041</v>
+        <v>56.5406162364401</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>26.46328001590309</v>
+        <v>14.69202921741931</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6335752630899438</v>
+        <v>1.182067471093819</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0140360818893899</v>
+        <v>0.08328613483382449</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1313</v>
+        <v>1402</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>550.3299316585474</v>
+        <v>655.5326019682666</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12.15</v>
+        <v>28.35</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.54061622823151</v>
+        <v>52.87658661350678</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>14.69202922157657</v>
+        <v>21.17613822259637</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.182067471093819</v>
+        <v>0.9042128713724186</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0832861348509962</v>
+        <v>0.0214796117140431</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1470</v>
+        <v>1315</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>547.7429036430694</v>
+        <v>649.8608423287941</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>24.05</v>
+        <v>66</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.10928301973557</v>
+        <v>59.38271391906461</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>9.792129262754566</v>
+        <v>32.15871326444631</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6276930334958327</v>
+        <v>0.8049966439350292</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.0560215217531132</v>
+        <v>-0.007150360713387</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1532</v>
+        <v>1416</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>543.2538055145982</v>
+        <v>645.1352497386905</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>23</v>
+        <v>11.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>58.97050386157714</v>
+        <v>61.94447938483959</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>20.29832270243194</v>
+        <v>30.85274104679664</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5816634189096864</v>
+        <v>0.1291138206485782</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.09881049609049281</v>
+        <v>0.0073388744044625</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1232</v>
+        <v>1558</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>541.2805406545077</v>
+        <v>615.7336306125093</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>157</v>
+        <v>103.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>55.69735301108717</v>
+        <v>68.15762579617778</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>27.80023536527266</v>
+        <v>28.85519666581038</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.5803411363815053</v>
+        <v>0.7450592151670029</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.0128097445623325</v>
+        <v>0.3419629449737953</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1434</v>
+        <v>1309</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>539.5527122806593</v>
+        <v>565.7642677191427</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>18.15</v>
+        <v>13.45</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.21804294143251</v>
+        <v>51.70261581230181</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>27.51394608831816</v>
+        <v>13.60120606297978</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.8818062890189259</v>
+        <v>1.840742268608321</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0553803818607723</v>
+        <v>0.1338613321081997</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1416</v>
+        <v>1459</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>535.1352497386905</v>
+        <v>563.6380660959044</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>11.8</v>
+        <v>15.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>61.94447918187806</v>
+        <v>77.4923470011735</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30.85274104360577</v>
+        <v>46.06660895597624</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.1291138206485782</v>
+        <v>0.4638066095904317</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0073388744521612</v>
+        <v>0.1024816875691817</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1305</v>
+        <v>1470</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>520.7341275304628</v>
+        <v>547.7429036430694</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>12.55</v>
+        <v>24.05</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.13699605271172</v>
+        <v>55.10928293021403</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>13.43374856038916</v>
+        <v>9.792129274672201</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.658078408327871</v>
+        <v>0.6276930334958327</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1193963203865519</v>
+        <v>-0.0560215216767948</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1504</v>
+        <v>1532</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>519.9917512800175</v>
+        <v>543.2538055145981</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>72.5</v>
+        <v>23</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.75028412009649</v>
+        <v>58.97050379523995</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>22.7687647936864</v>
+        <v>20.29832269870497</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4888935890894921</v>
+        <v>0.5816634189096864</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.2834299695150835</v>
+        <v>0.09881049609049281</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1319</v>
+        <v>1310</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>518.1908136414734</v>
+        <v>542.5811151445047</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>61.88554464906456</v>
+        <v>55.38948018115942</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>33.96063647720262</v>
+        <v>15.50465776488452</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4529857442042004</v>
+        <v>0.9245678145596484</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1868735329241295</v>
+        <v>0.133123222007933</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>516.9185159108955</v>
+        <v>541.2805406545077</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>25.7</v>
+        <v>157</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.76985931857707</v>
+        <v>55.69735298964808</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>22.82892279882</v>
+        <v>27.80023537858838</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6090170048012233</v>
+        <v>0.5803411363815053</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.019887632236574</v>
+        <v>-0.0128097446577299</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1409</v>
+        <v>1434</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>511.8726480343205</v>
+        <v>539.5527122806593</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>24.6</v>
+        <v>18.15</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>52.61131982208137</v>
+        <v>56.21804295370068</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>8.979191196028227</v>
+        <v>27.51394608831816</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.000864152994301</v>
+        <v>0.8818062890189259</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0936620202111229</v>
+        <v>0.0553803818416925</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1323</v>
+        <v>1229</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>510.7461759216433</v>
+        <v>537.3484779558407</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>21.35</v>
+        <v>41.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>57.96293930089447</v>
+        <v>53.25439133393905</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>22.70819238192509</v>
+        <v>17.61340624462151</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.3391232120837343</v>
+        <v>0.8449090978593103</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0346943249722699</v>
+        <v>0.0823428327393176</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1472</v>
+        <v>1236</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>510.1783441715651</v>
+        <v>536.9185159108955</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>90</v>
+        <v>25.7</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.08768279224792</v>
+        <v>61.76985937233094</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>8.672385844857823</v>
+        <v>22.82892283090387</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.371281264078221</v>
+        <v>0.6090170048012233</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-3.038710445495972</v>
+        <v>0.0198876322079517</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1104</v>
+        <v>1504</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>509.5001052637745</v>
+        <v>519.9917512800173</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>26.65</v>
+        <v>72.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>48.2712762816445</v>
+        <v>58.75028417952536</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>9.980424615995098</v>
+        <v>22.76876479469604</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7.847566730989209</v>
+        <v>0.4888935890894921</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0258262436593956</v>
+        <v>0.2834299693242861</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1316</v>
+        <v>1341</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>500.8040036876594</v>
+        <v>517.2937048698033</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>10.95</v>
+        <v>59.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.30173283982165</v>
+        <v>53.32788640560177</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.76857210521386</v>
+        <v>14.2197402102208</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6804003687659348</v>
+        <v>1.041815817960011</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0817244196552778</v>
+        <v>1.30509264941073</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1531</v>
+        <v>1409</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>491.6341760624841</v>
+        <v>511.8726480343204</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12.1</v>
+        <v>24.6</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>31.94818165625017</v>
+        <v>52.6113198273403</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>17.25825565074156</v>
+        <v>8.979191196028227</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3.910551899745749</v>
+        <v>1.000864152994301</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.0294132928528021</v>
+        <v>0.09366202018250409</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1102</v>
+        <v>1323</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>485.1839496974525</v>
+        <v>510.7461759216433</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>34.55</v>
+        <v>21.35</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>56.47887338580453</v>
+        <v>57.96293921812837</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>23.02219991031067</v>
+        <v>22.70819231607994</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7383610534235417</v>
+        <v>0.3391232120837343</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1836225307508999</v>
+        <v>-0.0346943249627278</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1442</v>
+        <v>1472</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>484.8355552765731</v>
+        <v>510.1783441715651</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>29.3</v>
+        <v>90</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>44.47882709635788</v>
+        <v>52.08768279061591</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>22.03642936010271</v>
+        <v>8.672385920497893</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.209353631031546</v>
+        <v>1.371281264078221</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.102951313034818</v>
+        <v>-3.038710445495972</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1314</v>
+        <v>1104</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>483.31988791893</v>
+        <v>509.5001052637745</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>8.18</v>
+        <v>26.65</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>55.26177636323113</v>
+        <v>48.27127637952903</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>18.86484359409071</v>
+        <v>9.980424610460783</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.9781652041917016</v>
+        <v>7.847566730989209</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0597974177922482</v>
+        <v>0.0258262435830784</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1110</v>
+        <v>1316</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>463.0720224604081</v>
+        <v>500.8040036876594</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15.95</v>
+        <v>10.95</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>49.28578481344542</v>
+        <v>54.30173290169277</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24.98405863300195</v>
+        <v>28.76857210603389</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.244737580115903</v>
+        <v>0.6804003687659348</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0295954261717669</v>
+        <v>0.0817244196171181</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1229</v>
+        <v>1314</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>462.3484779558407</v>
+        <v>493.31988791893</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>41.8</v>
+        <v>8.18</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.25439121852389</v>
+        <v>55.26177637337136</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.61340624049961</v>
+        <v>18.8648435970498</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8449090978593103</v>
+        <v>0.9781652041917016</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.08234283285380049</v>
+        <v>0.0597974177903409</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1456</v>
+        <v>1531</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>457.6969256993216</v>
+        <v>491.6341760624838</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>13.9</v>
+        <v>12.1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>50.87979298901983</v>
+        <v>31.94818173674802</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>19.5144439227252</v>
+        <v>17.25825585875508</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2.347210822789025</v>
+        <v>3.910551899745749</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0148895444970679</v>
+        <v>-0.0294132929481983</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1309</v>
+        <v>1102</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>445.7642677191427</v>
+        <v>485.1839496974525</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>13.45</v>
+        <v>34.55</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>51.70261579319898</v>
+        <v>56.47887341920018</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.60120600729013</v>
+        <v>23.02219992711577</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.840742268608321</v>
+        <v>0.7383610534235417</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1338613321272795</v>
+        <v>0.1836225306173429</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1514</v>
+        <v>1442</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>445.2274918078393</v>
+        <v>484.8355552765731</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>102</v>
+        <v>29.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46.55270296353722</v>
+        <v>44.47882720548265</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>20.58808632971599</v>
+        <v>22.03642938875876</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.097287880969369</v>
+        <v>1.209353631031546</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.8731045572935128</v>
+        <v>-0.1029513130157387</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1321</v>
+        <v>1582</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>442.3113323607615</v>
+        <v>473.4451743238308</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>32.25</v>
+        <v>76.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.29490565168209</v>
+        <v>56.93737990387199</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>16.68443285375906</v>
+        <v>18.06603093609629</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.571381605925785</v>
+        <v>1.083381020393677</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0580975194724809</v>
+        <v>0.7661654204847939</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1503</v>
+        <v>1110</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>435.3973627067965</v>
+        <v>463.0720224604081</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>200</v>
+        <v>15.95</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>47.47084294750952</v>
+        <v>49.28578503192432</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>17.29212852885826</v>
+        <v>24.98405870830702</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.255421574381364</v>
+        <v>1.244737580115903</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.349109500087487</v>
+        <v>-0.0295954263053245</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1513</v>
+        <v>1325</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>433.9597962205962</v>
+        <v>459.3417725390893</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>164</v>
+        <v>26.05</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>48.79186533831383</v>
+        <v>48.36360089369727</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>14.00989539931896</v>
+        <v>27.17222912237759</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.024415650226656</v>
+        <v>0.4087873172985314</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.2676095370090692</v>
+        <v>-0.0407717174964229</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1439</v>
+        <v>1456</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>433.2286326538189</v>
+        <v>457.6969256993216</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>29.2</v>
+        <v>13.9</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>58.59561898712856</v>
+        <v>50.87979303178086</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>10.5865159166464</v>
+        <v>19.51444391933353</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3505302747388419</v>
+        <v>2.347210822789025</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.1147782213631306</v>
+        <v>0.014889544420749</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1459</v>
+        <v>1514</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>423.6380660959043</v>
+        <v>445.2274918078393</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>15.5</v>
+        <v>102</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>77.49234688761229</v>
+        <v>46.5527030724695</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46.06660895597624</v>
+        <v>20.58808638103494</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4638066095904317</v>
+        <v>1.097287880969369</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.1024816876182299</v>
+        <v>0.8731045568165312</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1515</v>
+        <v>1321</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>410.8191001417828</v>
+        <v>442.3113323607615</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>33.4</v>
+        <v>32.25</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>50.39026754499157</v>
+        <v>49.29490563757236</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.33585719677528</v>
+        <v>16.68443294540323</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6179839332664308</v>
+        <v>1.571381605925785</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2962459867323244</v>
+        <v>0.0580975194343248</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1338</v>
+        <v>1220</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>401.6350022330085</v>
+        <v>437.3266647032893</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>14.5</v>
+        <v>10.75</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>38.28109747630435</v>
+        <v>26.92494424045886</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>44.00572424818365</v>
+        <v>29.36274941583552</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8903614351594671</v>
+        <v>2.068681956617276</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0133886267477511</v>
+        <v>-0.0011606088667777</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1541</v>
+        <v>1528</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>399.1796669808302</v>
+        <v>435.8683738944666</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>21.7</v>
+        <v>19.3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>49.49474319386185</v>
+        <v>49.37154329371873</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>22.4888939171554</v>
+        <v>23.89725361606732</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.984548341699249</v>
+        <v>0.9371265439687052</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0022927811467667</v>
+        <v>0.2345203799440345</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1340</v>
+        <v>1503</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>391.8291614429663</v>
+        <v>435.3973627067965</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>5.25</v>
+        <v>200</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52.16897840943749</v>
+        <v>47.4708429837008</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>16.91565337135247</v>
+        <v>17.2921285939485</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4857439824620488</v>
+        <v>1.255421574381364</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0246240329551341</v>
+        <v>1.349109499896689</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1233</v>
+        <v>1439</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>388.4122991503089</v>
+        <v>433.2286326538189</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>28.35</v>
+        <v>29.2</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>49.98494115503561</v>
+        <v>58.59561896665974</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22.23505368553241</v>
+        <v>10.58651581725217</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.449232343510168</v>
+        <v>0.3505302747388419</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0689772808594681</v>
+        <v>-0.1147782213440494</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1414</v>
+        <v>1524</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>388.0282085895051</v>
+        <v>431.9216208337951</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>19.4</v>
+        <v>27.35</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.08806457752396</v>
+        <v>51.69215630473526</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.05762977663172</v>
+        <v>15.46609499138192</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6215365584141244</v>
+        <v>0.5413413863104238</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.117322529139248</v>
+        <v>0.0940650038120267</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1210</v>
+        <v>1513</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>383.1265950975874</v>
+        <v>423.9597962205962</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>51.4</v>
+        <v>164</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>32.151416066241</v>
+        <v>48.79186535737665</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>31.60040389179836</v>
+        <v>14.00989541452508</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8673425439905668</v>
+        <v>1.024415650226656</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0290193217422376</v>
+        <v>0.2676095371044746</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1521</v>
+        <v>1515</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>376.6245021812778</v>
+        <v>410.8191001417828</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>25.95</v>
+        <v>33.4</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>57.14508781216642</v>
+        <v>50.39026755041714</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>14.19949514908023</v>
+        <v>22.33585722318728</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6184319372529795</v>
+        <v>0.6179839332664308</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.06866943401606131</v>
+        <v>0.2962459866846252</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1217</v>
+        <v>1338</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>374.4916518173558</v>
+        <v>401.6350022330086</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>9.99</v>
+        <v>14.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>54.31245240799242</v>
+        <v>38.28109734847306</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>14.97142570762492</v>
+        <v>44.00572422876437</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7117977007241904</v>
+        <v>0.8903614351594671</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0054446844359597</v>
+        <v>0.0133886267191325</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1569</v>
+        <v>1541</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>374.2819518429725</v>
+        <v>399.1796669808304</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>45.8</v>
+        <v>21.7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>57.89527472364782</v>
+        <v>49.49474324762368</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.266917288247</v>
+        <v>22.48889394080324</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.158090270549245</v>
+        <v>0.984548341699249</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.4560840962864699</v>
+        <v>-0.0022927811944646</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>369.8520699795409</v>
+        <v>391.8291614429663</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>42.8</v>
+        <v>5.25</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>36.81450108026442</v>
+        <v>52.16897849480701</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>18.08202531717924</v>
+        <v>16.91565339584542</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4271510007489493</v>
+        <v>0.4857439824620488</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.3283022988820937</v>
+        <v>0.0246240329398693</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1103</v>
+        <v>1233</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>368.4330404067546</v>
+        <v>388.4122991503085</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>13.2</v>
+        <v>28.35</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.64817947787704</v>
+        <v>49.98494122313653</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.55529895044476</v>
+        <v>22.23505372177094</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.165426115815074</v>
+        <v>1.449232343510168</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0167021000508247</v>
+        <v>0.0689772807736099</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>364.2764579220087</v>
+        <v>388.028208589505</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>65.7</v>
+        <v>19.4</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>49.50660103570655</v>
+        <v>51.08806476254867</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>15.34488868772903</v>
+        <v>20.05762987363504</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.538794496410854</v>
+        <v>0.6215365584141244</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1971384001158294</v>
+        <v>-0.117322529319094</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1310</v>
+        <v>1210</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>362.5811151445048</v>
+        <v>383.1265950975874</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>8.75</v>
+        <v>51.4</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>55.38948015600369</v>
+        <v>32.15141617066993</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.50465775503227</v>
+        <v>31.60040401966016</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9245678145596484</v>
+        <v>0.8673425439905668</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1331232220403683</v>
+        <v>-0.0290193220475144</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1227</v>
+        <v>1476</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>361.3825273899126</v>
+        <v>383.0644049678636</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>28.85</v>
+        <v>309</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.58838600277493</v>
+        <v>36.50354065681324</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>12.21852012811358</v>
+        <v>20.19794727085399</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.903912525594828</v>
+        <v>0.723270682934079</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0034033781601085</v>
+        <v>-1.276456930670031</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>359.4306516524555</v>
+        <v>376.6245021812778</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>67.7</v>
+        <v>25.95</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.06436945834152</v>
+        <v>57.14508787157128</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>21.21766611274101</v>
+        <v>14.19949512348561</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.043568124568368</v>
+        <v>0.6184319372529795</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.09967657327238889</v>
+        <v>0.06866943397790259</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1582</v>
+        <v>1225</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>358.4451743238308</v>
+        <v>376.6084494522893</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>76.5</v>
+        <v>25.7</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>56.93737979748308</v>
+        <v>52.18500291957083</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>18.06603092221954</v>
+        <v>27.00294867643328</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.083381020393677</v>
+        <v>0.4558883548668092</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.7661654206755842</v>
+        <v>0.2814756692075955</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1529</v>
+        <v>1217</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>356.8581998299717</v>
+        <v>374.4916518173558</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>17.1</v>
+        <v>9.99</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>41.25717720144066</v>
+        <v>54.31245240799242</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>37.07527200252561</v>
+        <v>14.97142573602887</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.306741232561975</v>
+        <v>0.7117977007241904</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1989074065188755</v>
+        <v>0.0054446844359597</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1533</v>
+        <v>1569</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>351.9446993029295</v>
+        <v>374.2819518429725</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>31.2</v>
+        <v>45.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>38.47670897014243</v>
+        <v>57.89527470377228</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>26.36042009305558</v>
+        <v>21.26691731733737</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.641530185092034</v>
+        <v>1.158090270549245</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1179621729878916</v>
+        <v>0.4560840962864699</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1325</v>
+        <v>1339</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>349.3417725390893</v>
+        <v>369.8520699795409</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>26.05</v>
+        <v>42.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.3636007524104</v>
+        <v>36.81450108349213</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>27.17222885506542</v>
+        <v>18.08202532682074</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4087873172985314</v>
+        <v>0.4271510007489493</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0407717173056267</v>
+        <v>-0.328302298901169</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1437</v>
+        <v>1103</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>347.3507379763628</v>
+        <v>368.4330404067547</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>32</v>
+        <v>13.2</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>59.15385440627125</v>
+        <v>48.64817958083941</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.13210735893479</v>
+        <v>12.55529898951685</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2680332083350446</v>
+        <v>1.165426115815074</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0367193952085406</v>
+        <v>0.0167021000126658</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1215</v>
+        <v>1419</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>341.6229399147849</v>
+        <v>364.2764579220088</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>107.5</v>
+        <v>65.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>43.99860458958428</v>
+        <v>49.50660094936831</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>21.42078599351252</v>
+        <v>15.34488875040709</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.583203627381015</v>
+        <v>0.538794496410854</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1477255905451818</v>
+        <v>0.1971384002303117</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1527</v>
+        <v>1466</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>339.6309623519664</v>
+        <v>363.1604401372727</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>32.7</v>
+        <v>15.95</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>44.62493953123995</v>
+        <v>45.88591711236042</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11.16940064515748</v>
+        <v>11.85888260162187</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5251284495345917</v>
+        <v>0.5271479186039677</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0156276432458697</v>
+        <v>-0.0506602766895121</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1417</v>
+        <v>1227</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>336.3024467419775</v>
+        <v>361.3825273899126</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>8.32</v>
+        <v>28.85</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.6980010524523</v>
+        <v>46.58838612540037</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>13.95605819595702</v>
+        <v>12.2185200645603</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.580664647372302</v>
+        <v>1.903912525594828</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0176531083122242</v>
+        <v>-0.0034033782745857</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1216</v>
+        <v>1525</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>333.7009954075111</v>
+        <v>359.4306516524555</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>76.2</v>
+        <v>67.7</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>48.41339413151415</v>
+        <v>52.06436954124105</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14.06257969069482</v>
+        <v>21.21766613633753</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.012445641427344</v>
+        <v>1.043568124568368</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0074686825851594</v>
+        <v>-0.0996765732342163</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1438</v>
+        <v>1529</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>333.6426828414448</v>
+        <v>356.8581998299718</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>22.4</v>
+        <v>17.1</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.39213185719917</v>
+        <v>41.25717740422801</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>9.004000475387732</v>
+        <v>37.07527198339947</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.9642709990733488</v>
+        <v>1.306741232561975</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0204999716903374</v>
+        <v>0.198907406423478</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1471</v>
+        <v>1533</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>332.8813879026658</v>
+        <v>351.9446993029295</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>9.83</v>
+        <v>31.2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>50.46921656562781</v>
+        <v>38.47670902877428</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>31.37636266516166</v>
+        <v>26.36042010507667</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5760971692811275</v>
+        <v>1.641530185092034</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.07811268923144191</v>
+        <v>0.1179621729592743</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1560</v>
+        <v>1437</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>327.5667896059923</v>
+        <v>347.3507379763628</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>683</v>
+        <v>32</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>48.48500317487468</v>
+        <v>59.15385440627125</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8.334497316102286</v>
+        <v>20.13210733783925</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.804985490078134</v>
+        <v>0.2680332083350446</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-1.543725682601526</v>
+        <v>0.0367193952085406</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>327.3266647032893</v>
+        <v>341.6229399147846</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>10.75</v>
+        <v>107.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>26.92494426552038</v>
+        <v>43.99860458958428</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>29.36274949990073</v>
+        <v>21.42078600437359</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2.068681956617276</v>
+        <v>1.583203627381015</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0011606088572386</v>
+        <v>0.1477255906405883</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1517</v>
+        <v>1527</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>326.4249110999143</v>
+        <v>339.6309623519664</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>11.25</v>
+        <v>32.7</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.68886178278572</v>
+        <v>44.62493960065289</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>37.39243781534834</v>
+        <v>11.16940069317089</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.176622164785267</v>
+        <v>0.5251284495345917</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0584021715330489</v>
+        <v>0.0156276431790923</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1519</v>
+        <v>1465</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>324.5868687041108</v>
+        <v>339.426895760053</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>729</v>
+        <v>12.05</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>52.14893876856885</v>
+        <v>42.22065156996601</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.73449779407408</v>
+        <v>20.63021124685189</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.361108074392777</v>
+        <v>1.230484462640645</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>5.888399933656729</v>
+        <v>-0.0029656247893289</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1524</v>
+        <v>1417</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>321.9216208337951</v>
+        <v>336.3024467419775</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>27.35</v>
+        <v>8.32</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>51.69215615107506</v>
+        <v>48.69800104204744</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.46609500360708</v>
+        <v>13.9560582621304</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5413413863104238</v>
+        <v>1.580664647372302</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0940650038692646</v>
+        <v>0.0176531083179477</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1528</v>
+        <v>1216</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>320.8683738944666</v>
+        <v>333.7009954075111</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>19.3</v>
+        <v>76.2</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.37154327775912</v>
+        <v>48.41339403309393</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>23.8972536296866</v>
+        <v>14.06257972485501</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.9371265439687052</v>
+        <v>1.012445641427344</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.2345203799726529</v>
+        <v>-0.0074686823752989</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1341</v>
+        <v>1438</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>317.2937048698033</v>
+        <v>333.6426828414448</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>59.8</v>
+        <v>22.4</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>53.32788640420505</v>
+        <v>51.39213201326394</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14.21974020887412</v>
+        <v>9.004000459825045</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.041815817960011</v>
+        <v>0.9642709990733488</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>1.305092649448893</v>
+        <v>-0.0204999717380343</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1213</v>
+        <v>1471</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>314.5030003607064</v>
+        <v>332.8813879026658</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>7.31</v>
+        <v>9.83</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>51.91069609813827</v>
+        <v>50.46921663990312</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11.05463234907972</v>
+        <v>31.37636268836397</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.1451978290477787</v>
+        <v>0.5760971692811275</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.1154500139776812</v>
+        <v>0.0781126891837418</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1219</v>
+        <v>1560</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>311.2821192706376</v>
+        <v>327.5667896059922</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>11.45</v>
+        <v>683</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.39022133747014</v>
+        <v>48.48500311133587</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>20.75190462790943</v>
+        <v>8.334497281689151</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3320764317982198</v>
+        <v>0.804985490078134</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.1035771631193878</v>
+        <v>-1.543725677831585</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1342</v>
+        <v>1517</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>310.5942915566644</v>
+        <v>326.4249110999143</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>103.5</v>
+        <v>11.25</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.39299343997044</v>
+        <v>46.68886175296845</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>17.15497268833231</v>
+        <v>37.39243788285044</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4582730554411717</v>
+        <v>0.176622164785267</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.4477887014566239</v>
+        <v>-0.0584021715139694</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1423</v>
+        <v>1519</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>304.956179991814</v>
+        <v>324.5868687041108</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>35.4</v>
+        <v>729</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.49364656782152</v>
+        <v>52.14893880120539</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16.23072283512996</v>
+        <v>14.73449771321825</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4945464668860674</v>
+        <v>1.361108074392777</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0816019866992177</v>
+        <v>5.888399935183166</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1324</v>
+        <v>1213</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>294.7513109295173</v>
+        <v>314.5030003607064</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>10.1</v>
+        <v>7.31</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>48.22618469543918</v>
+        <v>51.91069575948975</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>14.36021846706822</v>
+        <v>11.05463236302222</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6648904891574766</v>
+        <v>0.1451978290477787</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.025738113045745</v>
+        <v>0.1154500139872211</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1413</v>
+        <v>1219</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>292.1251922869555</v>
+        <v>311.2821192706376</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>11.45</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46.3643782405873</v>
+        <v>51.39022125845031</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8.816267549737805</v>
+        <v>20.75190472682829</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4036133516658232</v>
+        <v>0.3320764317982198</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0025238661475302</v>
+        <v>0.1035771631384677</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1256</v>
+        <v>1342</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>288.354818155947</v>
+        <v>310.5942915566644</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>181.5</v>
+        <v>103.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.63246546328</v>
+        <v>47.39299350892245</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>12.85382195601873</v>
+        <v>17.15497265722646</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>2.964061583190705</v>
+        <v>0.4582730554411717</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.8298861329490397</v>
+        <v>0.4477887011895094</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1530</v>
+        <v>1435</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>285.959035691042</v>
+        <v>308.3718068848086</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>28.7</v>
+        <v>21.6</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>47.83311934099936</v>
+        <v>45.0267210081437</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13.51126679131683</v>
+        <v>6.81837131721648</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6206378559536656</v>
+        <v>0.5023464084752423</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0402423620380063</v>
+        <v>-0.3053578316979793</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1477</v>
+        <v>1423</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>269.5530321282337</v>
+        <v>304.956179991814</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>194.5</v>
+        <v>35.4</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>32.86423444383541</v>
+        <v>45.49364021878144</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>24.05134215051272</v>
+        <v>16.23072049596693</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.7784344283048573</v>
+        <v>0.4945464668860674</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-1.241291889421542</v>
+        <v>0.0816019938253896</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1476</v>
+        <v>1324</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>268.064404967864</v>
+        <v>294.7513109295173</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>309</v>
+        <v>10.1</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>36.50354056865143</v>
+        <v>48.22618494055754</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>20.19794726100465</v>
+        <v>14.36021882498704</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.723270682934079</v>
+        <v>0.6648904891574766</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-1.276456927140357</v>
+        <v>0.0257381129885065</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1568</v>
+        <v>1413</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>265.3752331394645</v>
+        <v>292.1251922869555</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>28.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>44.72874448039149</v>
+        <v>46.36437807446351</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>11.93544365311626</v>
+        <v>8.816267580796573</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5988599273033973</v>
+        <v>0.4036133516658232</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.2312993381407224</v>
+        <v>-0.002523866109371</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1453</v>
+        <v>1256</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>264.8633635505189</v>
+        <v>288.354818155947</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>11.2</v>
+        <v>181.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>48.00077037531811</v>
+        <v>49.63246550430788</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>25.43614699491946</v>
+        <v>12.8538220283161</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.035084376673992</v>
+        <v>2.964061583190705</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0146059024001252</v>
+        <v>0.8298861324720692</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1225</v>
+        <v>1536</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>261.6084494522893</v>
+        <v>287.7096910593003</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>25.7</v>
+        <v>49.6</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>52.18500265879532</v>
+        <v>46.86208198174393</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>27.00294847845744</v>
+        <v>13.36482280086842</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4558883548668092</v>
+        <v>0.6465554034423079</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2814756693697651</v>
+        <v>-0.04909775773601</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1441</v>
+        <v>1530</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>261.5343351268805</v>
+        <v>285.959035691042</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>8.82</v>
+        <v>28.7</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.77165991066904</v>
+        <v>47.83311940865869</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.00735648503252</v>
+        <v>13.5112670023514</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.9406288262914252</v>
+        <v>0.6206378559536656</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0183440002374115</v>
+        <v>0.0402423619616893</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>253.3137378450076</v>
+        <v>269.5530321282337</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>20</v>
+        <v>194.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,49 +5322,49 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>49.27370935754189</v>
+        <v>32.86423447008231</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>7.344137410731241</v>
+        <v>24.05134213664953</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7175389722477784</v>
+        <v>0.7784344283048573</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0247048026026399</v>
+        <v>-1.241291889993921</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1466</v>
+        <v>1568</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>253.1604401372726</v>
+        <v>265.3752331394645</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>15.95</v>
+        <v>28.7</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.88591715452364</v>
+        <v>44.72874445122403</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>11.85888258761023</v>
+        <v>11.93544363671338</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5271479186039677</v>
+        <v>0.5988599273033973</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0506602767085938</v>
+        <v>0.2312993382074986</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>251.50326394856</v>
+        <v>264.8633635505189</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>11.45</v>
+        <v>11.2</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>51.12943429378935</v>
+        <v>48.00077033549425</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14.97077426823421</v>
+        <v>25.43614705399457</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.7636014300381918</v>
+        <v>1.035084376673992</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0040033331455449</v>
+        <v>0.0146059024001252</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1410</v>
+        <v>1441</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>248.5395880852266</v>
+        <v>261.5343351268805</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>24.3</v>
+        <v>8.82</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>34.68902257445971</v>
+        <v>43.77165985845689</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12.35081542241594</v>
+        <v>17.00735644552695</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>2.148893847908786</v>
+        <v>0.9406288262914252</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.1400628789451141</v>
+        <v>0.0183440002564903</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1516</v>
+        <v>1473</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>246.6226782739381</v>
+        <v>253.3137378450076</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>14.6</v>
+        <v>20</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.19018350809982</v>
+        <v>49.27370974574335</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>27.46762909149318</v>
+        <v>7.344137416064425</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.19243199087106</v>
+        <v>0.7175389722477784</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.3216303107046786</v>
+        <v>0.0247048024500028</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1436</v>
+        <v>1452</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>241.9612872599821</v>
+        <v>251.50326394856</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>38.45</v>
+        <v>11.45</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>47.66838981287747</v>
+        <v>51.1294341475173</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19.8284106775479</v>
+        <v>14.97077435355642</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3111930378637609</v>
+        <v>0.7636014300381918</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.3978120080206954</v>
+        <v>-0.0040033330883073</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1526</v>
+        <v>1410</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>235.6610551174353</v>
+        <v>248.5395880852266</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>16.3</v>
+        <v>24.3</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>44.20798779293111</v>
+        <v>34.68902246756522</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>24.59229553983974</v>
+        <v>12.35081542209755</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3760971958791139</v>
+        <v>2.148893847908786</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.2069504332666435</v>
+        <v>-0.1400628789164925</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1307</v>
+        <v>1516</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>233.0036356077617</v>
+        <v>246.6226782739381</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>30.55</v>
+        <v>14.6</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.99718728213294</v>
+        <v>49.19018354000374</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>22.15047530472348</v>
+        <v>27.46762907086844</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.769352971555548</v>
+        <v>0.19243199087106</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.07571732747117151</v>
+        <v>0.3216303106379001</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1467</v>
+        <v>1436</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>232.8355387179269</v>
+        <v>241.9612872599821</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>38.45</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>43.29201212871101</v>
+        <v>47.66838985727594</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>12.98053532820326</v>
+        <v>19.82841060938491</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6497057551196976</v>
+        <v>0.3111930378637609</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0647563286521715</v>
+        <v>0.3978120079252936</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1418</v>
+        <v>1526</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>229.8549230164984</v>
+        <v>235.6610551174353</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>17.75</v>
+        <v>16.3</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>42.48838939251804</v>
+        <v>44.20798782419934</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>15.77589067486845</v>
+        <v>24.59229559881399</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.230404005524862</v>
+        <v>0.3760971958791139</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0061799829840716</v>
+        <v>-0.2069504333048034</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1465</v>
+        <v>1307</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>229.426895760053</v>
+        <v>233.0036356077617</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>12.05</v>
+        <v>30.55</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>42.22065153070814</v>
+        <v>41.99718750843463</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>20.63021129541829</v>
+        <v>22.15047538384563</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.230484462640645</v>
+        <v>0.769352971555548</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0029656247702491</v>
+        <v>0.0757173271277409</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1451</v>
+        <v>1467</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>228.3924990372508</v>
+        <v>232.8355387179269</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>17.35</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>49.38124376634065</v>
+        <v>43.29201212871101</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.86832706078476</v>
+        <v>12.98053537438454</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.252204394830952</v>
+        <v>0.6497057551196976</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0178805929243976</v>
+        <v>-0.0647563286521715</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1538</v>
+        <v>1418</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>226.368746127909</v>
+        <v>229.8549230164984</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45.94801420178681</v>
+        <v>42.48838957028135</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>10.3725017862901</v>
+        <v>15.77589078800632</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.0014896469536719</v>
+        <v>1.230404005524862</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.1652492248084018</v>
+        <v>0.0061799829459133</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1537</v>
+        <v>1451</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>225.6267414798371</v>
+        <v>228.3924990372508</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>118.5</v>
+        <v>17.35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>24.56458740585927</v>
+        <v>49.38124369566484</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>28.6920969838955</v>
+        <v>18.86832703255653</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.745425971677168</v>
+        <v>1.252204394830952</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.6507229233081853</v>
+        <v>-0.0178805928957761</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1201</v>
+        <v>1538</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>223.7454027443056</v>
+        <v>226.368746127909</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>47.97641600488284</v>
+        <v>45.94801370108105</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>7.986529004976425</v>
+        <v>10.37250175790833</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.148395301031526</v>
+        <v>0.0014896469536719</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0052641088766894</v>
+        <v>-0.1652492196760304</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1540</v>
+        <v>1537</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>221.7013038493038</v>
+        <v>225.6267414798372</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>19.5</v>
+        <v>118.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>43.88841359724849</v>
+        <v>24.56458733908957</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>22.1338138267526</v>
+        <v>28.69209694910239</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.524139472162884</v>
+        <v>0.745425971677168</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,28 +6135,28 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.1102084469664124</v>
+        <v>-0.6507229233081853</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1454</v>
+        <v>1201</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>213.6881182101807</v>
+        <v>223.7454027443056</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>12.25</v>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>39.19855669702042</v>
+        <v>47.9764159350496</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>29.11323809342055</v>
+        <v>7.986528909534355</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.248594600866646</v>
+        <v>1.148395301031526</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0140713587273312</v>
+        <v>0.0052641088671491</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1447</v>
+        <v>1540</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>213.2878749054175</v>
+        <v>221.7013038493038</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>6.84</v>
+        <v>19.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>44.57645485689946</v>
+        <v>43.88841367952673</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.37320209625313</v>
+        <v>22.13381384111588</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.4800519718693842</v>
+        <v>0.524139472162884</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.009223033702000401</v>
+        <v>0.1102084469473322</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1536</v>
+        <v>1454</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>212.7096910593003</v>
+        <v>213.6881182101807</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>49.6</v>
+        <v>12.25</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46.8620819042408</v>
+        <v>39.19855659682874</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.36482282863286</v>
+        <v>29.113238135569</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.6465554034423079</v>
+        <v>1.248594600866646</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0490977575642863</v>
+        <v>-0.0140713587082511</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1109</v>
+        <v>1447</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>205.1056838203426</v>
+        <v>213.2878749054175</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>13.45</v>
+        <v>6.84</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>38.40650615618602</v>
+        <v>44.57645485381653</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>25.09808950193901</v>
+        <v>11.37320211323233</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.8643117574943694</v>
+        <v>0.4800519718693842</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0228848954169123</v>
+        <v>0.009223033698184</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1463</v>
+        <v>1109</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>202.2903562681361</v>
+        <v>205.1056838203426</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>17.3</v>
+        <v>13.45</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>37.01350870348875</v>
+        <v>38.40650615618602</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14.13916429534483</v>
+        <v>25.09808942783759</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.9736997827902302</v>
+        <v>0.8643117574943694</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0380891074107026</v>
+        <v>0.0228848953978322</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1522</v>
+        <v>1463</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>199.0900771095115</v>
+        <v>202.2903562681361</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>28</v>
+        <v>17.3</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>45.61042126022325</v>
+        <v>37.01350872196654</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.74205520315159</v>
+        <v>14.13916434967656</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5052217301558232</v>
+        <v>0.9736997827902302</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0709733455589495</v>
+        <v>-0.0380891074488618</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1446</v>
+        <v>1522</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>198.5057654994101</v>
+        <v>199.0900771095115</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>13.6</v>
+        <v>28</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>34.92801490214858</v>
+        <v>45.61042150577841</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>35.55865702556239</v>
+        <v>11.74205516570619</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.6608594136501045</v>
+        <v>0.5052217301558232</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0544294345771076</v>
+        <v>0.0709733453395365</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1435</v>
+        <v>1446</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>198.3718068848086</v>
+        <v>198.5057654994101</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>21.6</v>
+        <v>13.6</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>45.02670405717083</v>
+        <v>34.92801497678512</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>6.818365964751702</v>
+        <v>35.55865696028</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5023464084752423</v>
+        <v>0.6608594136501045</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,11 +6559,11 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.305357740016719</v>
+        <v>0.054429434558028</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>33.80146633714082</v>
+        <v>33.80146635919918</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>51.65440258564593</v>
+        <v>51.65440257766818</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.4971462874400563</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0474264733629165</v>
+        <v>0.0474264733533768</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>42.07617855653794</v>
+        <v>42.07617857370224</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.89218885458261</v>
+        <v>16.89218884421905</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.8447158840752654</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0090522833609971</v>
+        <v>0.0090522833514561</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>49.83674178223415</v>
+        <v>49.83674168097664</v>
       </c>
       <c r="I118" s="2" t="n">
         <v>14.75127686030053</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0051929199465477</v>
+        <v>0.0051929199847069</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>43.61889160814148</v>
+        <v>43.61889159514203</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>16.37014227465918</v>
+        <v>16.37014231891935</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.9744659909334394</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0856869067526944</v>
+        <v>-0.0856869068003896</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>43.3410424718312</v>
+        <v>43.3410423521948</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>14.28530699251195</v>
+        <v>14.28530687689071</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>1.770955723783036</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0061929820352749</v>
+        <v>0.0061929820448148</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>169.3052015115255</v>
+        <v>169.3052015115254</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>6.37</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>34.4185060191907</v>
+        <v>34.41850577408395</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>9.665101194934602</v>
+        <v>9.665101203818898</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.7672522892249104</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.013814981691874</v>
+        <v>-0.0138149816995062</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>42.27321884483177</v>
+        <v>42.27321910724249</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>10.33380478750228</v>
+        <v>10.33380496270166</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>1.01776883192692</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0043436426120009</v>
+        <v>0.004343642554763</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>42.59600189098128</v>
+        <v>42.59600196946278</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>12.13490597922264</v>
+        <v>12.1349061916649</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.3473014227915508</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0113506497123586</v>
+        <v>-0.0113506497218984</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>143.3722633573593</v>
+        <v>143.3722633573584</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>26.2</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>46.09680986324431</v>
+        <v>46.09681006015634</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.72399389964639</v>
+        <v>15.72399398105136</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.8282867803396481</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0550447814132848</v>
+        <v>0.0550447812892697</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>42.74243887120606</v>
+        <v>42.74243892073356</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>13.93286496894987</v>
+        <v>13.93286496055614</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.8852811865416521</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0180459786044927</v>
+        <v>0.0180459785873214</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>39.96511729653854</v>
+        <v>39.96511733708327</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>13.09209776252272</v>
+        <v>13.09209772052014</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.4213434617941936</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0336254392810015</v>
+        <v>0.0336254392428432</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>47.79652055457608</v>
+        <v>47.79652061576758</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>15.16495815135958</v>
+        <v>15.16495827992467</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>1.282125250815752</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0428448264630146</v>
+        <v>-0.0428448265011744</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>133.7499920217264</v>
+        <v>133.7499920217265</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>80.5</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>39.4814773891052</v>
+        <v>39.48147748724227</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>14.54599956863455</v>
+        <v>14.54599956283528</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.605663649081229</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.1517396244292548</v>
+        <v>0.1517396240476676</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>39.66830215050907</v>
+        <v>39.66830224959661</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>12.18500184301516</v>
+        <v>12.18500188542614</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.4418313634386131</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0460396909666792</v>
+        <v>-0.0460396909762193</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>110.7717791378498</v>
+        <v>110.7717791378497</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>24.35</v>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>49.14408512212886</v>
+        <v>49.14408515675712</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>7.074620456510342</v>
+        <v>7.074620490758845</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>1.114404924278646</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.1933121946057076</v>
+        <v>0.1933121945675476</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>39.55140400936919</v>
+        <v>39.55140419101584</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>11.35802988409606</v>
+        <v>11.35802997418333</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>1.317281133661583</v>
@@ -7442,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>40.41014459636456</v>
+        <v>40.41014455934047</v>
       </c>
       <c r="I132" s="2" t="n">
         <v>14.21995727583416</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>49.02681868291694</v>
+        <v>49.02681867832784</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>17.94835668618028</v>
+        <v>17.94835674910429</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.6862233948330496</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.2124328730582563</v>
+        <v>0.2124328730773337</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
